--- a/vlearn-app/public/quiz_excel/Day_05_AI Product Thinking _ Requirements/Day_05_Phan_01_20_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_05_AI Product Thinking _ Requirements/Day_05_Phan_01_20_Cau.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
@@ -1023,7 +1023,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thử nghiệm phải tạo bằng chứng trước khi đầu tư tự động hóa.</t>
+          <t>Các thành phần bắt buộc của thử nghiệm Wizard-of-Oz: Người sáng lập tạo biên bản thủ công phía sau giao diện (a), Ghi rõ quy trình thủ công và giới hạn của bằng chứng (b), Đo lường mức độ người dùng sử dụng/sẵn sàng trả tiền và chất lượng biên bản (c), và Đặt trước tiêu chí tiếp tục hoặc dừng thử nghiệm (e).</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1129,7 +1129,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Khía cạnh cần kiểm phải nối trực tiếp với lý do người dùng chưa đạt kết quả mong muốn.</t>
+          <t>Khi HR không hiểu vì sao ứng viên bị xếp thấp và không dám dùng kết quả, khía cạnh cần kiểm tra và cải thiện trước tiên là Mức độ tin cậy/khả năng giải thích (explainability) và Khả năng sử dụng (usability) của quyết định xếp hạng.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,3,4</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1182,7 +1182,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ quan sát có thể truy lại; loại ý kiến và suy đoán.</t>
+          <t>Bằng chứng cụ thể có thể kiểm chứng được: Câu truy vấn 'đặt vé tàu' -&gt; bot báo lỗi kèm ảnh chụp có timestamp (b), Luồng bình thường mã VN123 trả thông tin hành lý có nguồn (c), và Không thấy luồng sửa trong UI nên ghi rõ 'không quan sát được' (d). Nhận xét 'Bot khá ngu' (a) là cảm tính chủ quan.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1334,7 +1334,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cơ hội phải truy được về mẫu khó khăn của người dùng, không chỉ là tên lĩnh vực.</t>
+          <t>Khó khăn của người dùng là không biết chọn chuyên khoa nào khi đăng ký khám; cơ hội phù hợp là hỗ trợ quyết định bằng cách để AI hỏi một vài câu sàng lọc và gợi ý 2 chuyên khoa phù hợp, kèm cảnh báo và chuyển nhân viên y tế nếu có dấu hiệu nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1435,7 +1435,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một luồng từ đầu đến cuối phải nêu cả đường đi khi đủ và thiếu ngữ cảnh.</t>
+          <t>Luồng từ đầu đến cuối đầy đủ và an toàn nhất cho tính năng tóm tắt họp: Người dùng chọn Tạo -&gt; Lấy bản chép lời được phép (nếu thiếu thì báo/cho tải lên; nếu đủ thì tạo tóm tắt) -&gt; Người dùng xem lại/chỉnh sửa -&gt; Xác nhận xuất và lưu diff chỉnh sửa.</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1483,7 +1483,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm quy ước trả lời dữ liệu nào được và không được đọc.</t>
+          <t>Quy ước truy cập dữ liệu an toàn cho tính năng tóm tắt phiếu hỗ trợ: Kích hoạt khi nhân viên bấm; đầu vào là phiếu hỗ trợ; danh sách dữ liệu được phép gồm phiếu hỗ trợ và ba chính sách đã công bố; loại trừ hoàn toàn ghi chú riêng tư.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1538,7 +1538,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người kiểm tra phải có thể quyết định đạt/không đạt từ đầu ra và nguồn dữ liệu.</t>
+          <t>Các tiêu chí chấp nhận quan sát và kiểm thử được khách quan: Có tối đa 5 gạch đầu dòng (a), Mọi quyết định/hành động phải truy vết được tới bản chép lời (b), Không bịa người phụ trách/hạn chót (d), và Nếu không đạt tiêu chí quan trọng thì chuyển cho người kiểm tra (f). Tiêu chí 'AI thông minh' hay 'văn phong hoàn hảo' là mơ hồ, không kiểm thử được.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4,5</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -1593,7 +1593,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi tình huống phải kích hoạt một hành vi kỳ vọng khác.</t>
+          <t>Bộ tình huống bổ sung cho nhau đo lường các ranh giới khác nhau: Happy path hỏi hạn nộp bài A (a), Thiếu tên bài -&gt; hỏi lại (c), Hỏi ngoài phạm vi môn học -&gt; báo giới hạn/chuyển người (d), và Tài liệu chứa câu lệnh ghi đè -&gt; xử lý như nội dung dữ liệu, không tuân theo (e).</t>
         </is>
       </c>
     </row>
